--- a/cuisine.xlsx
+++ b/cuisine.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f7829a4895892f0f/astrbot_plugin_petitplanet_cuisine/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f7829a4895892f0f/astrbot_plugin_petitplanet_guide_x_x_xxx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6037861DBD103C4C8C6102036817A9EDA12D3DB1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C1B63EA-894E-4227-BDB7-8631706CE325}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_6037861DF390787A486102036817A9EDA12D3D84" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748B417C-2AEA-46E7-8048-A33C3D68443B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2664" windowWidth="21708" windowHeight="11016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="281">
   <si>
     <t>分类</t>
   </si>
@@ -373,7 +373,7 @@
     <t>素食/主食</t>
   </si>
   <si>
-    <t>番茄红宋汤(紫)</t>
+    <t>番笋红宋汤(紫)</t>
   </si>
   <si>
     <t>番茄(紫)</t>
@@ -463,9 +463,21 @@
     <t>钓鱼之力二阶</t>
   </si>
   <si>
+    <t>梦幻锦绣香蔬宴(金)</t>
+  </si>
+  <si>
+    <t>[蔬菜类](金)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
+    <t>梦幻三仙过海鱼(金)</t>
+  </si>
+  <si>
+    <t>[海鱼](金)</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
@@ -475,6 +487,9 @@
     <t>梦幻双色升鱼宴(紫)</t>
   </si>
   <si>
+    <t>[淡水鱼](金)</t>
+  </si>
+  <si>
     <t>[绿色蔬菜]</t>
   </si>
   <si>
@@ -568,9 +583,18 @@
     <t>110</t>
   </si>
   <si>
+    <t>水果烤虾拼盘(金)</t>
+  </si>
+  <si>
     <t>是的，*紫*色虾</t>
   </si>
   <si>
+    <t>梦幻奇迹蒜龙虾(金)</t>
+  </si>
+  <si>
+    <t>龙虾(金)</t>
+  </si>
+  <si>
     <t>大蒜</t>
   </si>
   <si>
@@ -595,6 +619,12 @@
     <t>[龙虾](紫)</t>
   </si>
   <si>
+    <t>梦幻*金*玉满堂饭(金)</t>
+  </si>
+  <si>
+    <t>水稻(金)</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
@@ -613,9 +643,24 @@
     <t>160</t>
   </si>
   <si>
+    <t>梦幻海贝海鲜烩(金)</t>
+  </si>
+  <si>
+    <t>[贝类](金)</t>
+  </si>
+  <si>
     <t>170</t>
   </si>
   <si>
+    <t>梦幻海岸虾鱼筵(金)</t>
+  </si>
+  <si>
+    <t>[鱼类](金)</t>
+  </si>
+  <si>
+    <t>梦幻鱼鲜寿司(金)</t>
+  </si>
+  <si>
     <t>180</t>
   </si>
   <si>
@@ -643,15 +688,30 @@
     <t>[黄色蔬菜]</t>
   </si>
   <si>
+    <t>梦幻草莓奶蛋糕(金)</t>
+  </si>
+  <si>
+    <t>草莓(金)</t>
+  </si>
+  <si>
     <t>大力撇三阶</t>
   </si>
   <si>
-    <t>牛奶</t>
+    <t>梦幻星莓漫游派(金)</t>
+  </si>
+  <si>
+    <t>蓝莓(金)</t>
   </si>
   <si>
     <t>大力撒三阶</t>
   </si>
   <si>
+    <t>梦幻番茄汤汁面(金)</t>
+  </si>
+  <si>
+    <t>番茄(金)</t>
+  </si>
+  <si>
     <t>自由烹饪</t>
   </si>
   <si>
@@ -673,12 +733,21 @@
     <t>[素菜]/[荤菜](紫)</t>
   </si>
   <si>
+    <t>梦幻什锦砂锅(金)</t>
+  </si>
+  <si>
+    <t>[素菜]/[荤菜](金)</t>
+  </si>
+  <si>
     <t>家常什锦饮</t>
   </si>
   <si>
     <t>珍稀什锦饮(紫)</t>
   </si>
   <si>
+    <t>梦幻什锦饮(金)</t>
+  </si>
+  <si>
     <t>家常什锦烧烤</t>
   </si>
   <si>
@@ -688,6 +757,9 @@
     <t>珍稀什锦烧烤(紫)</t>
   </si>
   <si>
+    <t>梦幻什锦烧烤(金)</t>
+  </si>
+  <si>
     <t>秘制菜</t>
   </si>
   <si>
@@ -724,7 +796,7 @@
     <t>荤菜(紫)</t>
   </si>
   <si>
-    <t>通过哈佩诺获得食谱_x000D_
+    <t>通过哈佩诺获得食谱_x000D__x000D_
 荤菜就是*紫*虾*紫*螃蟹什么的</t>
   </si>
   <si>
@@ -785,79 +857,16 @@
     <t>任务获得</t>
   </si>
   <si>
-    <t>梦幻锦绣香蔬宴(金)</t>
-  </si>
-  <si>
-    <t>[蔬菜类](金)</t>
-  </si>
-  <si>
-    <t>梦幻三仙过海鱼(金)</t>
-  </si>
-  <si>
-    <t>[海鱼](金)</t>
-  </si>
-  <si>
-    <t>[淡水鱼](金)</t>
-  </si>
-  <si>
-    <t>水果烤虾拼盘(金)</t>
-  </si>
-  <si>
-    <t>梦幻奇迹蒜龙虾(金)</t>
-  </si>
-  <si>
-    <t>龙虾(金)</t>
-  </si>
-  <si>
-    <t>梦幻*金*玉满堂饭(金)</t>
-  </si>
-  <si>
-    <t>水稻(金)</t>
-  </si>
-  <si>
-    <t>梦幻海贝海鲜烩(金)</t>
-  </si>
-  <si>
-    <t>[贝类](金)</t>
-  </si>
-  <si>
-    <t>梦幻海岸虾鱼筵(金)</t>
-  </si>
-  <si>
-    <t>[鱼类](金)</t>
-  </si>
-  <si>
-    <t>梦幻鱼鲜寿司(金)</t>
-  </si>
-  <si>
-    <t>梦幻草莓奶蛋糕(金)</t>
-  </si>
-  <si>
-    <t>草莓(金)</t>
-  </si>
-  <si>
-    <t>梦幻星莓漫游派(金)</t>
-  </si>
-  <si>
-    <t>蓝莓(金)</t>
-  </si>
-  <si>
-    <t>梦幻番茄汤汁面(金)</t>
-  </si>
-  <si>
-    <t>番茄(金)</t>
-  </si>
-  <si>
-    <t>梦幻什锦砂锅(金)</t>
-  </si>
-  <si>
-    <t>[素菜]/[荤菜](金)</t>
-  </si>
-  <si>
-    <t>梦幻什锦饮(金)</t>
-  </si>
-  <si>
-    <t>梦幻什锦烧烤(金)</t>
+    <t>小麦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[虾类](金)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[鱼类]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1242,9 +1251,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N105"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1288,7 +1300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1332,7 +1344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1376,7 +1388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1420,7 +1432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1464,7 +1476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1508,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1552,7 +1564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1596,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1640,7 +1652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1684,7 +1696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1728,7 +1740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1772,7 +1784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1816,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1860,7 +1872,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1904,7 +1916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1948,7 +1960,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1992,7 +2004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -2036,7 +2048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -2080,7 +2092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -2124,7 +2136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -2168,7 +2180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2212,7 +2224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -2256,7 +2268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -2300,7 +2312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -2344,7 +2356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -2388,7 +2400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2432,7 +2444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2476,7 +2488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -2520,7 +2532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -2564,7 +2576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -2608,7 +2620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -2652,7 +2664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -2696,7 +2708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -2740,7 +2752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -2784,7 +2796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -2828,7 +2840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -2872,7 +2884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -2916,7 +2928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -2960,7 +2972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -3004,7 +3016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>109</v>
       </c>
@@ -3048,7 +3060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>109</v>
       </c>
@@ -3092,7 +3104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>109</v>
       </c>
@@ -3136,7 +3148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>109</v>
       </c>
@@ -3180,7 +3192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>109</v>
       </c>
@@ -3224,7 +3236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>109</v>
       </c>
@@ -3268,7 +3280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>109</v>
       </c>
@@ -3312,7 +3324,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>109</v>
       </c>
@@ -3356,7 +3368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -3400,7 +3412,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -3444,7 +3456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>109</v>
       </c>
@@ -3488,12 +3500,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>109</v>
       </c>
       <c r="B52" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -3502,7 +3514,7 @@
         <v>119</v>
       </c>
       <c r="E52" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
         <v>13</v>
@@ -3511,7 +3523,7 @@
         <v>18</v>
       </c>
       <c r="H52" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I52" t="s">
         <v>50</v>
@@ -3532,15 +3544,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>109</v>
       </c>
       <c r="B53" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>151</v>
       </c>
       <c r="D53" t="s">
         <v>25</v>
@@ -3555,13 +3567,13 @@
         <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I53" t="s">
         <v>132</v>
       </c>
       <c r="J53" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K53" t="s">
         <v>13</v>
@@ -3576,21 +3588,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>109</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C54" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="D54" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -3599,13 +3611,13 @@
         <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I54" t="s">
         <v>62</v>
       </c>
       <c r="J54" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K54" t="s">
         <v>13</v>
@@ -3620,21 +3632,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F55" t="s">
         <v>13</v>
@@ -3664,12 +3676,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>109</v>
       </c>
       <c r="B56" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
         <v>41</v>
@@ -3708,15 +3720,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
         <v>113</v>
@@ -3752,21 +3764,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>109</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C58" t="s">
         <v>89</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E58" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
@@ -3796,12 +3808,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C59" t="s">
         <v>41</v>
@@ -3810,7 +3822,7 @@
         <v>92</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -3840,12 +3852,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
         <v>41</v>
@@ -3854,7 +3866,7 @@
         <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -3884,12 +3896,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C61" t="s">
         <v>46</v>
@@ -3928,15 +3940,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>109</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D62" t="s">
         <v>92</v>
@@ -3972,15 +3984,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>109</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C63" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D63" t="s">
         <v>92</v>
@@ -4016,12 +4028,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>109</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C64" t="s">
         <v>25</v>
@@ -4030,7 +4042,7 @@
         <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -4060,12 +4072,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>109</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C65" t="s">
         <v>53</v>
@@ -4104,18 +4116,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>109</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E66" t="s">
         <v>41</v>
@@ -4148,12 +4160,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>109</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
         <v>81</v>
@@ -4192,15 +4204,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>109</v>
       </c>
       <c r="B68" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C68" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D68" t="s">
         <v>33</v>
@@ -4236,12 +4248,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
@@ -4259,7 +4271,7 @@
         <v>94</v>
       </c>
       <c r="H69" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I69" t="s">
         <v>64</v>
@@ -4280,12 +4292,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>259</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
         <v>130</v>
@@ -4303,7 +4315,7 @@
         <v>94</v>
       </c>
       <c r="H70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I70" t="s">
         <v>104</v>
@@ -4312,7 +4324,7 @@
         <v>139</v>
       </c>
       <c r="K70" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L70" t="s">
         <v>21</v>
@@ -4324,18 +4336,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>109</v>
       </c>
       <c r="B71" t="s">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E71" t="s">
         <v>44</v>
@@ -4347,13 +4359,13 @@
         <v>94</v>
       </c>
       <c r="H71" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I71" t="s">
         <v>104</v>
       </c>
       <c r="J71" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K71" t="s">
         <v>13</v>
@@ -4368,12 +4380,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
         <v>41</v>
@@ -4385,7 +4397,7 @@
         <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
@@ -4412,12 +4424,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C73" t="s">
         <v>113</v>
@@ -4435,7 +4447,7 @@
         <v>18</v>
       </c>
       <c r="H73" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I73" t="s">
         <v>42</v>
@@ -4456,15 +4468,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D74" t="s">
         <v>55</v>
@@ -4479,7 +4491,7 @@
         <v>18</v>
       </c>
       <c r="H74" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I74" t="s">
         <v>62</v>
@@ -4500,15 +4512,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="D75" t="s">
         <v>68</v>
@@ -4523,13 +4535,13 @@
         <v>18</v>
       </c>
       <c r="H75" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I75" t="s">
         <v>42</v>
       </c>
       <c r="J75" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K75" t="s">
         <v>13</v>
@@ -4544,36 +4556,36 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="D76" t="s">
         <v>53</v>
       </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F76" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
       </c>
       <c r="H76" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="I76" t="s">
         <v>42</v>
       </c>
       <c r="J76" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K76" t="s">
         <v>13</v>
@@ -4588,15 +4600,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="C77" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="D77" t="s">
         <v>25</v>
@@ -4611,13 +4623,13 @@
         <v>18</v>
       </c>
       <c r="H77" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I77" t="s">
         <v>62</v>
       </c>
       <c r="J77" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K77" t="s">
         <v>13</v>
@@ -4632,15 +4644,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B78" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D78" t="s">
         <v>44</v>
@@ -4649,19 +4661,19 @@
         <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>33</v>
+        <v>280</v>
       </c>
       <c r="G78" t="s">
         <v>18</v>
       </c>
       <c r="H78" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I78" t="s">
         <v>57</v>
       </c>
       <c r="J78" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K78" t="s">
         <v>13</v>
@@ -4676,15 +4688,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B79" t="s">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="C79" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="D79" t="s">
         <v>89</v>
@@ -4699,13 +4711,13 @@
         <v>18</v>
       </c>
       <c r="H79" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="I79" t="s">
         <v>64</v>
       </c>
       <c r="J79" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K79" t="s">
         <v>13</v>
@@ -4720,12 +4732,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
         <v>141</v>
@@ -4743,13 +4755,13 @@
         <v>94</v>
       </c>
       <c r="H80" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I80" t="s">
         <v>97</v>
       </c>
       <c r="J80" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="K80" t="s">
         <v>13</v>
@@ -4764,12 +4776,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C81" t="s">
         <v>118</v>
@@ -4778,16 +4790,16 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="G81" t="s">
         <v>94</v>
       </c>
       <c r="H81" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I81" t="s">
         <v>95</v>
@@ -4808,36 +4820,36 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B82" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C82" t="s">
         <v>91</v>
       </c>
       <c r="D82" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E82" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F82" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G82" t="s">
         <v>94</v>
       </c>
       <c r="H82" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I82" t="s">
         <v>42</v>
       </c>
       <c r="J82" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="K82" t="s">
         <v>13</v>
@@ -4852,15 +4864,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="C83" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="D83" t="s">
         <v>92</v>
@@ -4875,13 +4887,13 @@
         <v>94</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I83" t="s">
         <v>97</v>
       </c>
       <c r="J83" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="K83" t="s">
         <v>13</v>
@@ -4896,18 +4908,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B84" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="C84" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="D84" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -4919,13 +4931,13 @@
         <v>94</v>
       </c>
       <c r="H84" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I84" t="s">
         <v>97</v>
       </c>
       <c r="J84" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K84" t="s">
         <v>13</v>
@@ -4940,21 +4952,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B85" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="C85" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="D85" t="s">
         <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F85" t="s">
         <v>92</v>
@@ -4963,13 +4975,13 @@
         <v>18</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I85" t="s">
         <v>42</v>
       </c>
       <c r="J85" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K85" t="s">
         <v>13</v>
@@ -4984,18 +4996,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B86" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C86" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D86" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -5010,10 +5022,10 @@
         <v>56</v>
       </c>
       <c r="I86" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J86" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K86" t="s">
         <v>13</v>
@@ -5028,18 +5040,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B87" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="D87" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E87" t="s">
         <v>13</v>
@@ -5054,10 +5066,10 @@
         <v>78</v>
       </c>
       <c r="I87" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J87" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K87" t="s">
         <v>13</v>
@@ -5072,18 +5084,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="D88" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E88" t="s">
         <v>13</v>
@@ -5095,13 +5107,13 @@
         <v>18</v>
       </c>
       <c r="H88" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I88" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J88" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K88" t="s">
         <v>13</v>
@@ -5116,18 +5128,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D89" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E89" t="s">
         <v>13</v>
@@ -5145,7 +5157,7 @@
         <v>20</v>
       </c>
       <c r="J89" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K89" t="s">
         <v>13</v>
@@ -5160,18 +5172,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D90" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
@@ -5189,7 +5201,7 @@
         <v>20</v>
       </c>
       <c r="J90" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K90" t="s">
         <v>13</v>
@@ -5204,18 +5216,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="D91" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
@@ -5227,13 +5239,13 @@
         <v>84</v>
       </c>
       <c r="H91" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I91" t="s">
         <v>20</v>
       </c>
       <c r="J91" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K91" t="s">
         <v>13</v>
@@ -5248,18 +5260,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B92" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D92" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E92" t="s">
         <v>13</v>
@@ -5274,10 +5286,10 @@
         <v>56</v>
       </c>
       <c r="I92" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="J92" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K92" t="s">
         <v>13</v>
@@ -5292,18 +5304,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B93" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C93" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -5318,10 +5330,10 @@
         <v>78</v>
       </c>
       <c r="I93" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="J93" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K93" t="s">
         <v>13</v>
@@ -5336,18 +5348,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="C94" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E94" t="s">
         <v>13</v>
@@ -5359,13 +5371,13 @@
         <v>94</v>
       </c>
       <c r="H94" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I94" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="J94" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K94" t="s">
         <v>13</v>
@@ -5380,12 +5392,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B95" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C95" t="s">
         <v>119</v>
@@ -5412,7 +5424,7 @@
         <v>48</v>
       </c>
       <c r="K95" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="L95" t="s">
         <v>21</v>
@@ -5424,12 +5436,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B96" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
@@ -5438,7 +5450,7 @@
         <v>119</v>
       </c>
       <c r="E96" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
@@ -5456,7 +5468,7 @@
         <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="L96" t="s">
         <v>21</v>
@@ -5468,21 +5480,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B97" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C97" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="D97" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="E97" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
@@ -5494,13 +5506,13 @@
         <v>138</v>
       </c>
       <c r="I97" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="J97" t="s">
         <v>13</v>
       </c>
       <c r="K97" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="L97" t="s">
         <v>21</v>
@@ -5512,15 +5524,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B98" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D98" t="s">
         <v>46</v>
@@ -5544,7 +5556,7 @@
         <v>13</v>
       </c>
       <c r="K98" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="L98" t="s">
         <v>21</v>
@@ -5556,12 +5568,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B99" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s">
         <v>141</v>
@@ -5588,7 +5600,7 @@
         <v>48</v>
       </c>
       <c r="K99" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="L99" t="s">
         <v>21</v>
@@ -5600,18 +5612,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B100" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C100" t="s">
         <v>74</v>
       </c>
       <c r="D100" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
@@ -5632,7 +5644,7 @@
         <v>51</v>
       </c>
       <c r="K100" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="L100" t="s">
         <v>21</v>
@@ -5644,12 +5656,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B101" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C101" t="s">
         <v>41</v>
@@ -5676,7 +5688,7 @@
         <v>13</v>
       </c>
       <c r="K101" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="L101" t="s">
         <v>21</v>
@@ -5688,12 +5700,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B102" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C102" t="s">
         <v>77</v>
@@ -5714,13 +5726,13 @@
         <v>138</v>
       </c>
       <c r="I102" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="J102" t="s">
         <v>13</v>
       </c>
       <c r="K102" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="L102" t="s">
         <v>21</v>
@@ -5732,15 +5744,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B103" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="C103" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="D103" t="s">
         <v>13</v>
@@ -5761,30 +5773,30 @@
         <v>13</v>
       </c>
       <c r="J103" t="s">
+        <v>270</v>
+      </c>
+      <c r="K103" t="s">
+        <v>271</v>
+      </c>
+      <c r="L103" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" t="s">
+        <v>13</v>
+      </c>
+      <c r="N103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>246</v>
       </c>
-      <c r="K103" t="s">
-        <v>247</v>
-      </c>
-      <c r="L103" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" t="s">
-        <v>13</v>
-      </c>
-      <c r="N103" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>222</v>
-      </c>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C104" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="D104" t="s">
         <v>120</v>
@@ -5802,13 +5814,13 @@
         <v>13</v>
       </c>
       <c r="I104" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="J104" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="K104" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="L104" t="s">
         <v>21</v>
@@ -5820,12 +5832,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B105" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C105" t="s">
         <v>41</v>
@@ -5852,7 +5864,7 @@
         <v>13</v>
       </c>
       <c r="K105" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="L105" t="s">
         <v>21</v>
@@ -5868,7 +5880,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N51 A55:N69 A52 C52:D52 F52:N52 A53 D53:N53 A54:B54 D54:N54 A72:N74 A70 C70:N70 A71 D71:N71 A80:N82 A75 D75:N75 A76:B76 D76:N76 A77 D77:N77 A78 D78:N78 A79 D79:N79 A86:N87 A83 D83:N83 A84 D84:N84 A85 D85:N85 A89:N90 A88 D88:N88 A92:N93 A91 D91:N91 A95:N105 A94 D94:N94" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N77 A85:N105 A84:C84 E84:N84 A79:N83 A78:B78 D78:E78 G78:N78" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>